--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:57</t>
+    <t xml:space="preserve">2026-08-02 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:47</t>
+    <t xml:space="preserve">2026-08-05 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:41</t>
+    <t xml:space="preserve">2026-08-16 09:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:52</t>
+    <t xml:space="preserve">2026-08-19 12:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:25</t>
+    <t xml:space="preserve">2026-08-28 11:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:34</t>
+    <t xml:space="preserve">2026-09-06 17:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
